--- a/trustfl.xlsx
+++ b/trustfl.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC7A38BE-349A-4178-A6AC-2D710E60CA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D030F991-3EBF-4B36-BF95-BBB1AA73DAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="577">
   <si>
     <t>polarity</t>
   </si>
@@ -475,12 +475,6 @@
     <t>লাল রঙের পোশাকটি আরামদায়ক স্টাইলিশ সাইজটি দারুণভাবে ফিট হয়েছে কাউল নেকের নকশাটিও খুব সুন্দর পুরো দাম দিয়েও কেনার যোগ্য</t>
   </si>
   <si>
-    <t>খুব ভালোবাসি</t>
-  </si>
-  <si>
-    <t>ফোনটি দ্রুত পৌঁছেছে ভালো লেগেছে</t>
-  </si>
-  <si>
     <t>একটি খুব ভালো ফোন দ্রুত কাজ সত্যই দুর্দান্ত</t>
   </si>
   <si>
@@ -491,12 +485,6 @@
   </si>
   <si>
     <t>খুবই ভালো অবস্থায় ফোনটি এসেছে পাওয়ার শুরু করলাম সবকিছু চলছে দিনের ওয়ারেন্টি পাওয়ায় ভালো লাগছে বছরের পুরানো ফোনের একটি সাশ্রয়ী ভালো বিকল্প</t>
-  </si>
-  <si>
-    <t>পণ্যটি একদম নিখুঁত</t>
-  </si>
-  <si>
-    <t>পণ্যটি দুর্দান্ত</t>
   </si>
   <si>
     <t>ফোনটি অনবদ্য দুর্দান্ত অবস্থায় রয়েছে প্রকৃতপক্ষে ফোনটি একেবারে নতুন নতুন সংস্কার করা হয়নি বিদেশে ব্যবহারের উপহার কিনেছিলেন স্থানীয় নেটওয়ার্ক সিস্টেমের পুরোপুরি খাপ খাইয়ে কাজ</t>
@@ -2125,7 +2113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B578"/>
+  <dimension ref="A1:B574"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="59.453125" customWidth="1"/>
@@ -2134,7 +2122,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -4497,7 +4485,7 @@
         <v>297</v>
       </c>
       <c r="B296" t="s">
-        <v>102</v>
+        <v>2</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
@@ -4505,7 +4493,7 @@
         <v>298</v>
       </c>
       <c r="B297" t="s">
-        <v>102</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
@@ -4513,7 +4501,7 @@
         <v>299</v>
       </c>
       <c r="B298" t="s">
-        <v>102</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
@@ -4521,7 +4509,7 @@
         <v>300</v>
       </c>
       <c r="B299" t="s">
-        <v>102</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
@@ -6209,7 +6197,7 @@
         <v>511</v>
       </c>
       <c r="B510" t="s">
-        <v>2</v>
+        <v>102</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
@@ -6217,7 +6205,7 @@
         <v>512</v>
       </c>
       <c r="B511" t="s">
-        <v>2</v>
+        <v>102</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
@@ -6225,7 +6213,7 @@
         <v>513</v>
       </c>
       <c r="B512" t="s">
-        <v>2</v>
+        <v>102</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
@@ -6233,7 +6221,7 @@
         <v>514</v>
       </c>
       <c r="B513" t="s">
-        <v>2</v>
+        <v>102</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
@@ -6721,38 +6709,6 @@
         <v>575</v>
       </c>
       <c r="B574" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="575" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A575" t="s">
-        <v>576</v>
-      </c>
-      <c r="B575" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="576" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A576" t="s">
-        <v>577</v>
-      </c>
-      <c r="B576" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="577" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A577" t="s">
-        <v>578</v>
-      </c>
-      <c r="B577" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="578" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A578" t="s">
-        <v>579</v>
-      </c>
-      <c r="B578" t="s">
         <v>102</v>
       </c>
     </row>
